--- a/line_campaign/12月勉強会_LINE配信_入力シート.xlsx
+++ b/line_campaign/12月勉強会_LINE配信_入力シート.xlsx
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="322">
   <si>
     <r>
       <rPr>
@@ -5003,7 +5003,7 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="str">
         <f aca="false">"未記入："&amp;COUNTIF(配信スケジュール!$P$3:$P$59,"未記入")&amp;" 通"</f>
-        <v>未記入：57 通</v>
+        <v>未記入：47 通</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6916,9 +6916,7 @@
       <c r="M50" s="17"/>
       <c r="N50" s="17"/>
       <c r="O50" s="17"/>
-      <c r="P50" s="18" t="s">
-        <v>44</v>
-      </c>
+      <c r="P50" s="18"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="n">
@@ -6941,9 +6939,7 @@
       <c r="M51" s="17"/>
       <c r="N51" s="17"/>
       <c r="O51" s="17"/>
-      <c r="P51" s="18" t="s">
-        <v>44</v>
-      </c>
+      <c r="P51" s="18"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="n">
@@ -6966,9 +6962,7 @@
       <c r="M52" s="17"/>
       <c r="N52" s="17"/>
       <c r="O52" s="17"/>
-      <c r="P52" s="18" t="s">
-        <v>44</v>
-      </c>
+      <c r="P52" s="18"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="n">
@@ -6991,9 +6985,7 @@
       <c r="M53" s="17"/>
       <c r="N53" s="17"/>
       <c r="O53" s="17"/>
-      <c r="P53" s="18" t="s">
-        <v>44</v>
-      </c>
+      <c r="P53" s="18"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="n">
@@ -7016,9 +7008,7 @@
       <c r="M54" s="17"/>
       <c r="N54" s="17"/>
       <c r="O54" s="17"/>
-      <c r="P54" s="18" t="s">
-        <v>44</v>
-      </c>
+      <c r="P54" s="18"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="n">
@@ -7041,9 +7031,7 @@
       <c r="M55" s="17"/>
       <c r="N55" s="17"/>
       <c r="O55" s="17"/>
-      <c r="P55" s="18" t="s">
-        <v>44</v>
-      </c>
+      <c r="P55" s="18"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="13" t="n">
@@ -7066,9 +7054,7 @@
       <c r="M56" s="17"/>
       <c r="N56" s="17"/>
       <c r="O56" s="17"/>
-      <c r="P56" s="18" t="s">
-        <v>44</v>
-      </c>
+      <c r="P56" s="18"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="n">
@@ -7091,9 +7077,7 @@
       <c r="M57" s="17"/>
       <c r="N57" s="17"/>
       <c r="O57" s="17"/>
-      <c r="P57" s="18" t="s">
-        <v>44</v>
-      </c>
+      <c r="P57" s="18"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="n">
@@ -7116,9 +7100,7 @@
       <c r="M58" s="17"/>
       <c r="N58" s="17"/>
       <c r="O58" s="17"/>
-      <c r="P58" s="18" t="s">
-        <v>44</v>
-      </c>
+      <c r="P58" s="18"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="n">
@@ -7141,9 +7123,7 @@
       <c r="M59" s="17"/>
       <c r="N59" s="17"/>
       <c r="O59" s="17"/>
-      <c r="P59" s="18" t="s">
-        <v>44</v>
-      </c>
+      <c r="P59" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P59"/>

--- a/line_campaign/12月勉強会_LINE配信_入力シート.xlsx
+++ b/line_campaign/12月勉強会_LINE配信_入力シート.xlsx
@@ -88,7 +88,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="D30" authorId="0">
+    <comment ref="D40" authorId="0">
       <text>
         <r>
           <rPr>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="360">
   <si>
     <r>
       <rPr>
@@ -3810,7 +3810,412 @@
     <t xml:space="preserve">参加特典</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IELTS 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技能 現在地診断シート</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【診断・分析】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シート</t>
+  </si>
+  <si>
     <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スコアレポート分析シート</t>
+  </si>
+  <si>
+    <t xml:space="preserve">今の勉強法チェックリスト</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">停滞する人のパターン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">時間の棚卸しシート</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標の言語化シート</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">半年で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逆算ロードマップ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【計画・記録】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週間計画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">振り返りシート</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">学習ログシート</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模試計画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スコア推移シート</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">試験日逆算カレンダー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">次アクションシート</t>
+  </si>
+  <si>
+    <t xml:space="preserve">採点基準の読み方ガイド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【ライティング】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自己添削チェックリスト</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">添削ログ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">間違いノート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">シート</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の答案比較解剖資料</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">アイデア発想法ガイド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ライティング練習の組み方ガイド</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">T/F/NG </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">判定フローチャート</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【リーディング・リスニング】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">解く順</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間配分ガイド</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">間違い原因分類シート</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ディクテーション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日間メニュー</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">シャドーイング段階別ガイド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ひとりスピーキング練習メニュー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【スピーキング】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スピーキング失点セルフ分析シート</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Part 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">準備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分の考え方ガイド</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">習慣設計ガイド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【継続・導線】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">挫折分岐シート</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週間お試しコーチング体験券</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">招待・体験</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コミュニティ招待券</t>
   </si>
   <si>
     <t xml:space="preserve">参加特典の数（自動）</t>
@@ -7831,7 +8236,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -8006,11 +8411,17 @@
       <c r="B9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="C9" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="F9" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G9" s="17"/>
     </row>
@@ -8021,11 +8432,17 @@
       <c r="B10" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="C10" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="F10" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G10" s="17"/>
     </row>
@@ -8036,11 +8453,17 @@
       <c r="B11" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="C11" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>247</v>
+      </c>
       <c r="F11" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G11" s="17"/>
     </row>
@@ -8051,11 +8474,17 @@
       <c r="B12" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="C12" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>247</v>
+      </c>
       <c r="F12" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G12" s="17"/>
     </row>
@@ -8066,11 +8495,17 @@
       <c r="B13" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="C13" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="F13" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G13" s="17"/>
     </row>
@@ -8081,11 +8516,17 @@
       <c r="B14" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
+      <c r="C14" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="F14" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G14" s="17"/>
     </row>
@@ -8096,11 +8537,17 @@
       <c r="B15" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="C15" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>247</v>
+      </c>
       <c r="F15" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G15" s="17"/>
     </row>
@@ -8111,11 +8558,17 @@
       <c r="B16" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="C16" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="F16" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G16" s="17"/>
     </row>
@@ -8126,11 +8579,17 @@
       <c r="B17" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="C17" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="F17" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G17" s="17"/>
     </row>
@@ -8141,11 +8600,17 @@
       <c r="B18" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="C18" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="F18" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G18" s="17"/>
     </row>
@@ -8156,11 +8621,17 @@
       <c r="B19" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="C19" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="F19" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G19" s="17"/>
     </row>
@@ -8171,11 +8642,17 @@
       <c r="B20" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="C20" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="F20" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G20" s="17"/>
     </row>
@@ -8186,11 +8663,17 @@
       <c r="B21" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="C21" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>247</v>
+      </c>
       <c r="F21" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G21" s="17"/>
     </row>
@@ -8201,11 +8684,17 @@
       <c r="B22" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="C22" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>247</v>
+      </c>
       <c r="F22" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G22" s="17"/>
     </row>
@@ -8216,11 +8705,17 @@
       <c r="B23" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="C23" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="F23" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G23" s="17"/>
     </row>
@@ -8231,11 +8726,17 @@
       <c r="B24" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="C24" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>247</v>
+      </c>
       <c r="F24" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G24" s="17"/>
     </row>
@@ -8246,11 +8747,17 @@
       <c r="B25" s="16" t="n">
         <v>17</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="C25" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>247</v>
+      </c>
       <c r="F25" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G25" s="17"/>
     </row>
@@ -8261,11 +8768,17 @@
       <c r="B26" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="C26" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>247</v>
+      </c>
       <c r="F26" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G26" s="17"/>
     </row>
@@ -8276,11 +8789,17 @@
       <c r="B27" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="C27" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>247</v>
+      </c>
       <c r="F27" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G27" s="17"/>
     </row>
@@ -8291,21 +8810,237 @@
       <c r="B28" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
+      <c r="C28" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>247</v>
+      </c>
       <c r="F28" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G28" s="17"/>
     </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B29" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G29" s="17"/>
+    </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="D30" s="13" t="n">
-        <f aca="false">COUNTIFS(A3:A28,"参加特典",C3:C28,"&lt;&gt;")</f>
-        <v>0</v>
+      <c r="A30" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B30" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G30" s="17"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B31" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G31" s="17"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B32" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G32" s="17"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B33" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G33" s="17"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G34" s="17"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G35" s="17"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B36" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G36" s="17"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B37" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G37" s="17"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B38" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G38" s="17"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <f aca="false">COUNTIFS(A3:A38,"参加特典",C3:C38,"&lt;&gt;")</f>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -8341,34 +9076,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>267</v>
+        <v>305</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8376,36 +9111,36 @@
         <v>32</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>278</v>
+        <v>316</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -8419,7 +9154,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -8433,7 +9168,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -8447,7 +9182,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -8461,7 +9196,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -8475,7 +9210,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -8489,7 +9224,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -8503,7 +9238,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -8551,25 +9286,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8577,27 +9312,27 @@
         <v>32</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>227</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -8608,7 +9343,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>303</v>
+        <v>341</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -8619,7 +9354,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -8630,7 +9365,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -8641,7 +9376,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -8652,7 +9387,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -8663,7 +9398,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -8674,7 +9409,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -8685,7 +9420,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -8696,7 +9431,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -8707,7 +9442,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -8718,7 +9453,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -8729,7 +9464,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -8740,7 +9475,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -8751,7 +9486,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -8762,7 +9497,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -8773,7 +9508,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -8784,7 +9519,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -8795,7 +9530,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -8806,7 +9541,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>

--- a/line_campaign/12月勉強会_LINE配信_入力シート.xlsx
+++ b/line_campaign/12月勉強会_LINE配信_入力シート.xlsx
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="361">
   <si>
     <r>
       <rPr>
@@ -3863,7 +3863,48 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">時間の棚卸しシート</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社会人が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間をつくる 時間の棚卸しシート</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">目標の言語化シート</t>
@@ -3892,7 +3933,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">逆算ロードマップ</t>
+      <t xml:space="preserve">逆算ロードマップ（試験日逆算カレンダー付き）</t>
     </r>
   </si>
   <si>
@@ -3922,11 +3963,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">振り返りシート</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">学習ログシート</t>
+      <t xml:space="preserve">学習ログシート</t>
+    </r>
   </si>
   <si>
     <r>
@@ -3956,13 +3994,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">試験日逆算カレンダー</t>
-  </si>
-  <si>
     <t xml:space="preserve">次アクションシート</t>
   </si>
   <si>
-    <t xml:space="preserve">採点基準の読み方ガイド</t>
+    <t xml:space="preserve">試験官はここを見ている 採点基準の読み方ガイド</t>
   </si>
   <si>
     <t xml:space="preserve">【ライティング】</t>
@@ -4051,7 +4086,40 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">アイデア発想法ガイド</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Task 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で手が止まらない アイデア発想法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">パターン</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ライティング練習の組み方ガイド</t>
@@ -4106,7 +4174,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">間違い原因分類シート</t>
+    <t xml:space="preserve">「なんとなく間違えた」をなくす 間違い原因分類シート</t>
   </si>
   <si>
     <r>
@@ -4139,7 +4207,57 @@
     <t xml:space="preserve">シャドーイング段階別ガイド</t>
   </si>
   <si>
-    <t xml:space="preserve">ひとりスピーキング練習メニュー</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分 ひとりスピーキング練習メニュー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日分</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">【スピーキング】</t>
@@ -4184,15 +4302,164 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">習慣設計ガイド</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を試験官にする </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Speaking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模擬試験プロンプト集</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">活用】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Writing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自己添削 プロンプト集（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Task 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で自分専用の単語帳をつくる プロンプト集</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">習慣設計＆挫折分岐ガイド</t>
   </si>
   <si>
     <t xml:space="preserve">【継続・導線】</t>
   </si>
   <si>
-    <t xml:space="preserve">挫折分岐シート</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -4208,7 +4475,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">週間お試しコーチング体験券</t>
+      <t xml:space="preserve">週間お試しコーチング体験券（先着○名）</t>
     </r>
   </si>
   <si>
@@ -8530,7 +8797,7 @@
       </c>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
         <v>260</v>
       </c>
@@ -8614,7 +8881,7 @@
       </c>
       <c r="G18" s="17"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
         <v>260</v>
       </c>
@@ -8625,10 +8892,10 @@
         <v>275</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>263</v>
+        <v>276</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>247</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>264</v>
@@ -8643,13 +8910,13 @@
         <v>12</v>
       </c>
       <c r="C20" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>276</v>
       </c>
-      <c r="D20" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>263</v>
+      <c r="E20" s="17" t="s">
+        <v>247</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>264</v>
@@ -8664,13 +8931,13 @@
         <v>13</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>247</v>
+        <v>276</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>263</v>
       </c>
       <c r="F21" s="13" t="s">
         <v>264</v>
@@ -8684,11 +8951,11 @@
       <c r="B22" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>279</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>247</v>
@@ -8698,21 +8965,21 @@
       </c>
       <c r="G22" s="17"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
         <v>260</v>
       </c>
       <c r="B23" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="17" t="s">
         <v>280</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>263</v>
+        <v>276</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>247</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>264</v>
@@ -8726,11 +8993,11 @@
       <c r="B24" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="18" t="s">
         <v>281</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>247</v>
@@ -8747,11 +9014,11 @@
       <c r="B25" s="16" t="n">
         <v>17</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="17" t="s">
         <v>282</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>247</v>
@@ -8769,10 +9036,10 @@
         <v>18</v>
       </c>
       <c r="C26" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="D26" s="18" t="s">
         <v>283</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>278</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>247</v>
@@ -8782,21 +9049,21 @@
       </c>
       <c r="G26" s="17"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
         <v>260</v>
       </c>
       <c r="B27" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="C27" s="17" t="s">
-        <v>284</v>
+      <c r="C27" s="18" t="s">
+        <v>285</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>247</v>
+        <v>283</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>263</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>264</v>
@@ -8814,7 +9081,7 @@
         <v>286</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>247</v>
@@ -8835,28 +9102,28 @@
         <v>287</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>263</v>
+        <v>283</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>247</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>264</v>
       </c>
       <c r="G29" s="17"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
         <v>260</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>22</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="17" t="s">
         <v>288</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>247</v>
@@ -8874,13 +9141,13 @@
         <v>23</v>
       </c>
       <c r="C31" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="D31" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="D31" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>247</v>
+      <c r="E31" s="18" t="s">
+        <v>263</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>264</v>
@@ -8894,11 +9161,11 @@
       <c r="B32" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="C32" s="18" t="s">
-        <v>290</v>
+      <c r="C32" s="17" t="s">
+        <v>291</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>247</v>
@@ -8908,28 +9175,28 @@
       </c>
       <c r="G32" s="17"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
         <v>260</v>
       </c>
       <c r="B33" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="17" t="s">
         <v>292</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>263</v>
+        <v>293</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>247</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>264</v>
       </c>
       <c r="G33" s="17"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
         <v>260</v>
       </c>
@@ -8937,10 +9204,10 @@
         <v>26</v>
       </c>
       <c r="C34" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="D34" s="18" t="s">
         <v>293</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>291</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>247</v>
@@ -8957,11 +9224,11 @@
       <c r="B35" s="16" t="n">
         <v>27</v>
       </c>
-      <c r="C35" s="18" t="s">
-        <v>294</v>
+      <c r="C35" s="17" t="s">
+        <v>295</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>247</v>
@@ -8982,10 +9249,10 @@
         <v>296</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>263</v>
+        <v>297</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>247</v>
       </c>
       <c r="F36" s="13" t="s">
         <v>264</v>
@@ -9000,13 +9267,13 @@
         <v>29</v>
       </c>
       <c r="C37" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="D37" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="D37" s="18" t="s">
-        <v>295</v>
-      </c>
       <c r="E37" s="18" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F37" s="13" t="s">
         <v>264</v>
@@ -9021,13 +9288,13 @@
         <v>30</v>
       </c>
       <c r="C38" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>299</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>298</v>
       </c>
       <c r="F38" s="13" t="s">
         <v>264</v>
@@ -9036,7 +9303,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C40" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D40" s="13" t="n">
         <f aca="false">COUNTIFS(A3:A38,"参加特典",C3:C38,"&lt;&gt;")</f>
@@ -9076,34 +9343,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9111,36 +9378,36 @@
         <v>32</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -9154,7 +9421,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -9168,7 +9435,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -9182,7 +9449,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -9196,7 +9463,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -9210,7 +9477,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -9224,7 +9491,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -9238,7 +9505,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -9286,25 +9553,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9312,27 +9579,27 @@
         <v>32</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>227</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -9343,7 +9610,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -9354,7 +9621,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -9365,7 +9632,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -9376,7 +9643,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -9387,7 +9654,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -9398,7 +9665,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -9409,7 +9676,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -9420,7 +9687,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -9431,7 +9698,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -9442,7 +9709,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -9453,7 +9720,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -9464,7 +9731,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -9475,7 +9742,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -9486,7 +9753,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -9497,7 +9764,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -9508,7 +9775,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -9519,7 +9786,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -9530,7 +9797,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -9541,7 +9808,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>

--- a/line_campaign/12月勉強会_LINE配信_入力シート.xlsx
+++ b/line_campaign/12月勉強会_LINE配信_入力シート.xlsx
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="390">
   <si>
     <r>
       <rPr>
@@ -3671,6 +3671,33 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）社会人から</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IELTS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に挑戦し、人生が変わった自分のストーリー</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">音声</t>
   </si>
   <si>
@@ -3721,6 +3748,50 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年にスコアを取り切るために、まず決めるべき</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つのこと</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">12/11</t>
   </si>
   <si>
@@ -3751,12 +3822,42 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）多くの人が気づかずにハマる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つの落とし穴と抜け出し方</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">12/12</t>
   </si>
   <si>
     <t xml:space="preserve">○名以上を指導して分かったスコアアップの本当のカギ</t>
   </si>
   <si>
+    <t xml:space="preserve">（仮）たくさんの受講生を見てきて分かった、伸びる人の共通点</t>
+  </si>
+  <si>
     <t xml:space="preserve">12/15</t>
   </si>
   <si>
@@ -3804,9 +3905,73 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時代でも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IELTS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・英語を学ぶ価値と、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">との付き合い方</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">いちばん伝えたいメッセージ</t>
   </si>
   <si>
+    <t xml:space="preserve">（仮）勉強会の前に、いちばん伝えたい想い</t>
+  </si>
+  <si>
     <t xml:space="preserve">参加特典</t>
   </si>
   <si>
@@ -3829,7 +3994,48 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">【診断・分析】</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【診断・分析】各技能の今のスコア・目標・得意</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">苦手を書き出し、どこから伸ばすかを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">枚で見える化。勉強会当日のワークでも使用</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">シート</t>
@@ -3841,6 +4047,9 @@
     <t xml:space="preserve">スコアレポート分析シート</t>
   </si>
   <si>
+    <t xml:space="preserve">（仮）【診断・分析】公式スコアレポートの数字から、どの技能・どの採点項目が足を引っ張っているかを読み解く記入式シート</t>
+  </si>
+  <si>
     <t xml:space="preserve">今の勉強法チェックリスト</t>
   </si>
   <si>
@@ -3850,6 +4059,33 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">（仮）【診断・分析】今の勉強が「スコアにつながる勉強」になっているかを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">項目でセルフチェック</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">停滞する人のパターン</t>
     </r>
     <r>
@@ -3869,6 +4105,67 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">（仮）【診断・分析】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で止まる人に共通する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の勉強パターンと、それぞれの抜け出し方</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">社会人が</t>
     </r>
     <r>
@@ -3907,6 +4204,33 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【診断・分析】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週間の時間の使い方を書き出し、勉強に回せるすき間時間を見つける</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">目標の言語化シート</t>
   </si>
   <si>
@@ -3916,6 +4240,33 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">（仮）【診断・分析】「なぜ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IELTS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か」「いつまでに何点か」「取れたら何をするか」を言葉にして、続ける理由をつくる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">半年で</t>
     </r>
     <r>
@@ -3937,7 +4288,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">【計画・記録】</t>
+    <t xml:space="preserve">（仮）【計画・記録】試験日から逆算して、月ごと・週ごとにやることを決めるロードマップ。カレンダーに書き込んで使う</t>
   </si>
   <si>
     <r>
@@ -3973,6 +4324,50 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">（仮）【計画・記録】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週間の計画と、毎日の学習記録・振り返りを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">枚で管理</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">模試計画</t>
     </r>
     <r>
@@ -3994,13 +4389,84 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">（仮）【計画・記録】模試をいつ解くかの計画と、技能別スコアの推移をグラフで記録</t>
+  </si>
+  <si>
     <t xml:space="preserve">次アクションシート</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【計画・記録】勉強会で学んだことから、明日からの具体的な行動を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つに絞って書き出す（勉強会の最後に使用）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">試験官はここを見ている 採点基準の読み方ガイド</t>
   </si>
   <si>
-    <t xml:space="preserve">【ライティング】</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【ライティング】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Writing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つの採点基準（課題達成・一貫性・語彙・文法）を、日本人向けにかみくだいて解説</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">自己添削チェックリスト</t>
@@ -4012,6 +4478,33 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">（仮）【ライティング】書き終わった答案を自分で見直すためのチェック項目。採点基準の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">項目ごとに整理</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">添削ログ</t>
     </r>
     <r>
@@ -4050,6 +4543,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">（仮）【ライティング】添削で指摘されたミスを種類ごとに記録し、同じミスを繰り返さないための記録シート</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -4089,6 +4585,67 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【ライティング】同じ設問の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">答案と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">答案を並べ、どこで点差がついたかを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">文ずつ解説</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -4122,12 +4679,66 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【ライティング】設問を見て意見・理由・具体例を素早く出すための考え方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つ（答え・例文は載せない）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">ライティング練習の組み方ガイド</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【ライティング】時間を計って書く→見直す→書き直す、の練習サイクルと</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週間の回し方</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -4144,7 +4755,31 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">【リーディング・リスニング】</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【リーディング・リスニング】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">True / False / Not Given </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を迷わず判定するための手順をフローチャートで</t>
+    </r>
   </si>
   <si>
     <r>
@@ -4174,9 +4809,56 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【リーディング・リスニング】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Reading</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Listening</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で、どの順番で解き、どこに何分かけるかの考え方</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">「なんとなく間違えた」をなくす 間違い原因分類シート</t>
   </si>
   <si>
+    <t xml:space="preserve">（仮）【リーディング・リスニング】間違えた問題を「単語」「文構造」「設問の読み違い」など原因別に分類し、弱点を特定する</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -4204,9 +4886,107 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【リーディング・リスニング】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Listening</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">力を上げるディクテーションを、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日間のメニューに</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">シャドーイング段階別ガイド</t>
   </si>
   <si>
+    <t xml:space="preserve">（仮）【リーディング・リスニング】聞く→つぶやく→重ねる→シャドーイング、と段階を踏んで進めるやり方と素材の選び方</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -4260,7 +5040,82 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">【スピーキング】</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【スピーキング】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人でできるスピーキング練習を、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日分のメニューに（お題のみ・回答例なし）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">スピーキング失点セルフ分析シート</t>
@@ -4269,6 +5124,33 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【スピーキング】自分の回答を録音して聞き直し、採点基準の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">項目ごとに失点ポイントを書き出す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -4305,6 +5187,33 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【スピーキング】トピックカードを見てから話し始めるまでの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分間で、何をメモし、どう組み立てるか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -4344,7 +5253,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">【</t>
+      <t xml:space="preserve">（仮）【</t>
     </r>
     <r>
       <rPr>
@@ -4363,6 +5272,57 @@
       </rPr>
       <t xml:space="preserve">活用】</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ChatGPT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">等に試験官役をさせ、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Part 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の模擬面接とフィードバックを受けるためのプロンプト集</t>
+    </r>
   </si>
   <si>
     <r>
@@ -4438,6 +5398,14 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -4450,14 +5418,94 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">活用】自分の答案を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に読ませ、採点基準の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">項目ごとに弱点を指摘してもらうプロンプト集（スコア判定ではなく弱点発見用）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">で自分専用の単語帳をつくる プロンプト集</t>
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">活用】自分の答案や間違えた問題から、覚えるべき語彙を抜き出して単語帳にするプロンプト集</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">習慣設計＆挫折分岐ガイド</t>
   </si>
   <si>
-    <t xml:space="preserve">【継続・導線】</t>
+    <t xml:space="preserve">（仮）【継続・導線】勉強を習慣にする仕組みと、「忙しい」「伸びない」など挫折しそうな時の立て直し方</t>
   </si>
   <si>
     <r>
@@ -4479,10 +5527,40 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（仮）【継続・導線】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週間、学習計画へのアドバイスと進捗チェックを体験できる券（先着○名・人数は要決定）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">招待・体験</t>
   </si>
   <si>
     <t xml:space="preserve">コミュニティ招待券</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（仮）【継続・導線】一緒に学ぶ仲間とつながれるコミュニティへの招待（無料／有料・内容は要決定）</t>
   </si>
   <si>
     <t xml:space="preserve">参加特典の数（自動）</t>
@@ -8557,7 +9635,7 @@
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
         <v>248</v>
       </c>
@@ -8567,12 +9645,14 @@
       <c r="C3" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="18" t="s">
+        <v>250</v>
+      </c>
       <c r="E3" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G3" s="17"/>
     </row>
@@ -8584,18 +9664,20 @@
         <v>2</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="D4" s="17"/>
+        <v>253</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>254</v>
+      </c>
       <c r="E4" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G4" s="17"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
         <v>248</v>
       </c>
@@ -8603,14 +9685,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="D5" s="17"/>
+        <v>256</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>257</v>
+      </c>
       <c r="E5" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G5" s="17"/>
     </row>
@@ -8622,14 +9706,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="D6" s="17"/>
+        <v>259</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>260</v>
+      </c>
       <c r="E6" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G6" s="17"/>
     </row>
@@ -8641,14 +9727,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="D7" s="17"/>
+        <v>262</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="E7" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G7" s="17"/>
     </row>
@@ -8660,650 +9748,652 @@
         <v>6</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="D8" s="17"/>
+        <v>264</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>265</v>
+      </c>
       <c r="E8" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G8" s="17"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G9" s="17"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G10" s="17"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G11" s="17"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>4</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>5</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G13" s="17"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>6</v>
       </c>
       <c r="C14" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>263</v>
-      </c>
       <c r="F14" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G14" s="17"/>
     </row>
-    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G15" s="17"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>8</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G16" s="17"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>9</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G17" s="17"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>11</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G19" s="17"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G20" s="17"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B21" s="16" t="n">
         <v>13</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G21" s="17"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B22" s="16" t="n">
         <v>14</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B23" s="16" t="n">
         <v>15</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G23" s="17"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B24" s="16" t="n">
         <v>16</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G24" s="17"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B25" s="16" t="n">
         <v>17</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G25" s="17"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B26" s="16" t="n">
         <v>18</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G26" s="17"/>
     </row>
-    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B27" s="16" t="n">
         <v>19</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G27" s="17"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B28" s="16" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G28" s="17"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B29" s="16" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G29" s="17"/>
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>22</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G30" s="17"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B31" s="16" t="n">
         <v>23</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G31" s="17"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B32" s="16" t="n">
         <v>24</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G32" s="17"/>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B33" s="16" t="n">
         <v>25</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G33" s="17"/>
     </row>
-    <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B34" s="16" t="n">
         <v>26</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G34" s="17"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B35" s="16" t="n">
         <v>27</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G35" s="17"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B36" s="16" t="n">
         <v>28</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="E36" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G36" s="17"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B37" s="16" t="n">
         <v>29</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G37" s="17"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B38" s="16" t="n">
         <v>30</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G38" s="17"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C40" s="20" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="D40" s="13" t="n">
         <f aca="false">COUNTIFS(A3:A38,"参加特典",C3:C38,"&lt;&gt;")</f>
@@ -9343,34 +10433,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9378,36 +10468,36 @@
         <v>32</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>320</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -9421,7 +10511,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -9435,7 +10525,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -9449,7 +10539,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -9463,7 +10553,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -9477,7 +10567,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -9491,7 +10581,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -9505,7 +10595,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -9553,25 +10643,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>332</v>
+        <v>361</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9579,27 +10669,27 @@
         <v>32</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>227</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -9610,7 +10700,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -9621,7 +10711,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -9632,7 +10722,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -9643,7 +10733,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -9654,7 +10744,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -9665,7 +10755,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -9676,7 +10766,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -9687,7 +10777,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -9698,7 +10788,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -9709,7 +10799,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -9720,7 +10810,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -9731,7 +10821,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -9742,7 +10832,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -9753,7 +10843,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -9764,7 +10854,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>356</v>
+        <v>385</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -9775,7 +10865,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -9786,7 +10876,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -9797,7 +10887,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -9808,7 +10898,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>

--- a/line_campaign/12月勉強会_LINE配信_入力シート.xlsx
+++ b/line_campaign/12月勉強会_LINE配信_入力シート.xlsx
@@ -10,13 +10,15 @@
   <sheets>
     <sheet name="使い方" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="配信スケジュール" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="型の説明" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="基本情報" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="特典" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="受講生事例" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="素材リスト" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="準備Todo" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="型の説明" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="基本情報" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="特典" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="受講生事例" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="素材リスト" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">準備Todo!$A$1:$L$38</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">配信スケジュール!$A$1:$P$59</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -82,7 +84,57 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">締切日の週の月曜日。週ごとに並べ替え・絞り込みに使えます</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">締切までの日数。赤＝締切を過ぎた未完了、黄＝締切まで</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">日以内</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -105,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="491">
   <si>
     <r>
       <rPr>
@@ -148,6 +200,42 @@
   </si>
   <si>
     <t xml:space="preserve">■ このシートの使い方</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「準備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Todo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」シートで、いつまでに何を準備するかを確認・管理する（締切を過ぎた未完了は赤くなります）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1830,6 +1918,1882 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">で人生を動かしましょう</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">週（月曜）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カテゴリ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">やること</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何に使う（配信・場面）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">初回使用日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要なもの・メモ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作業予定日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">完了日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残り日数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">方針決め</t>
+  </si>
+  <si>
+    <t xml:space="preserve">勉強会のあとの流れを決める（講座の内容・期間・価格、個別相談の枠数）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全配信のゴール／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降の個別相談案内</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">これが決まると配信全体の言葉選びが決まる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未着手</t>
+  </si>
+  <si>
+    <t xml:space="preserve">勉強会タイトルを確定する</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">正式告知／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LP</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">基本情報シートに記入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開始時刻・所要時間・各回の定員を決める</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">正式告知／申込ボタン</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仮：両日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">当日学べること</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つを確定する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中身の予告／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LP</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">勉強会スライドの骨子にもなる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自己紹介ストーリー（短文）を書く</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11/30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">予告／先行特典①</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">実績の数字を集める（指導人数・スコアの伸びなど実数のみ）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11/30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">予告／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">募集開始</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">受講生への確認が必要なものは早めに</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「基本情報」シートを全部埋める</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全配信文の作成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特典・導線</t>
+  </si>
+  <si>
+    <t xml:space="preserve">体験券の先着人数と内容を決める</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">特典初公開</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">特典シート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">No.29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の「○名」を更新</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">コミュニティの形を決める（無料</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">有料・場所）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">特典シート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">No.30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を更新</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">特典の渡し方と時期を決める（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で一括</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ダウンロードページ）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">勉強会当日〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/22</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大特典のタイトルを最終確定する</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">特典シート</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">先行予約特典</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本の話す内容をメモする</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜 先行特典配信</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">特典シートの（仮）を更新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">素材</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受講生に対談・掲載を依頼し、許可を取る（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">対談動画／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/17 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受講生の声</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">受講生事例シートに記入</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大特典のサムネイル（デザイン統一）を作る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">特典初公開／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/20 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チラ見せ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Canva</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">でテンプレを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つ作って使い回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大特典の一覧画像を作る</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">素材リストに登録</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">価値提供動画①「</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IELTS 0→6.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ロードマップ」を撮る（既存動画の流用も可）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">価値提供</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">対談動画①を撮る</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受講生の逆転劇</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">勉強会の詳細</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を作る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">募集開始</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">対談動画②（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Speaking</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）を撮る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">事例</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">限定音声（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">正式告知の</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P.S.</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用）を録る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">正式告知</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Speaking</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">クイズ動画「</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">秒で答えられますか？」を撮る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/13 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参加型</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Writing</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">動画（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Task 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で点が伸びない原因など）を撮る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/16 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">価値提供</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">答え・例文は渡さない方針で</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受講生の声（画像）とショート動画</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本を集める</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受講生の声／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/17 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">募集明日まで</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">先行特典①〜③の音声を録る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ステップのタグを作る（申込済</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未申込</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">先行特典受取</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参加済 など）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">セグメント配信全般</t>
+  </si>
+  <si>
+    <t xml:space="preserve">先行特典④〜⑥の音声を録る</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">まとめて公開</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">日程選択ボタン・日程変更ボタン・申込完了メッセージを作る</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zoom</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ミーティングを</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回分発行する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/21 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">開催案内</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">基本情報シートにリンクを記入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オープンチャットを作る（作る場合）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込完了メッセージ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配信準備</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配信スケジュールの</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Phase 1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11/30</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/8</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）を記入し、</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Claude</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に文面を作ってもらう</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11/30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の配信</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ステータスを「記入済」に</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Phase 1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の配信を予約し、自分宛てにテスト配信する（リンク確認）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11/30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">初回配信</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月前半</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Phase 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/18</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）の文面作成・配信予約</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の配信</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技能 現在地診断シート」を先に完成させる（当日ワーク用）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/19 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">勉強会当日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大特典の中身を完成させる</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">勉強会のあと配布</t>
+  </si>
+  <si>
+    <t xml:space="preserve">個別相談の予約枠・申込フォームを準備する</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降の個別相談案内</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Phase 4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/19</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜）の文面作成・配信予約</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜の配信</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">勉強会スライドの完成・リハーサル</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月中に骨子だけ作っておくと楽</t>
     </r>
   </si>
   <si>
@@ -6253,7 +8217,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6334,6 +8298,18 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6355,7 +8331,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6403,6 +8379,33 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -6429,7 +8432,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -6441,11 +8444,11 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFE7E6E6"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -6468,6 +8471,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -6651,7 +8658,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:B24"/>
+  <dimension ref="B1:B26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -6692,38 +8699,38 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2"/>
+      <c r="B13" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -6743,35 +8750,46 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="2"/>
+      <c r="B19" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="B20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="2" t="str">
+      <c r="B21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="2" t="str">
         <f aca="false">"未記入："&amp;COUNTIF(配信スケジュール!$P$3:$P$59,"未記入")&amp;" 通"</f>
         <v>未記入：47 通</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="2" t="str">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="2" t="str">
         <f aca="false">"記入済："&amp;COUNTIF(配信スケジュール!$P$3:$P$59,"記入済")&amp;" 通"</f>
         <v>記入済：0 通</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="2" t="str">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="2" t="str">
         <f aca="false">"作成済："&amp;COUNTIF(配信スケジュール!$P$3:$P$59,"作成済")&amp;" 通"</f>
         <v>作成済：0 通</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="2" t="str">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="2" t="str">
         <f aca="false">"配信済："&amp;COUNTIF(配信スケジュール!$P$3:$P$59,"配信済")&amp;" 通"</f>
         <v>配信済：0 通</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="2" t="str">
+        <f aca="false">"準備Todo 完了："&amp;COUNTIF(準備Todo!$J$2:$J$38,"完了")&amp;" / "&amp;COUNTA(準備Todo!$D$2:$D$38)&amp;" 件"</f>
+        <v>準備Todo 完了：0 / 37 件</v>
       </c>
     </row>
   </sheetData>
@@ -6811,60 +8829,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>46356</v>
@@ -6874,36 +8892,36 @@
         <v>月</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
       <c r="M2" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6911,7 +8929,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="15" t="n">
         <v>46356</v>
@@ -6921,16 +8939,16 @@
         <v>月</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
@@ -6940,7 +8958,7 @@
       <c r="N3" s="17"/>
       <c r="O3" s="17"/>
       <c r="P3" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6948,7 +8966,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>46357</v>
@@ -6958,16 +8976,16 @@
         <v>火</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
@@ -6977,7 +8995,7 @@
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
       <c r="P4" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6985,7 +9003,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>46358</v>
@@ -6995,16 +9013,16 @@
         <v>水</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
@@ -7014,7 +9032,7 @@
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
       <c r="P5" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7022,7 +9040,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="15" t="n">
         <v>46358</v>
@@ -7032,16 +9050,16 @@
         <v>水</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
@@ -7051,7 +9069,7 @@
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
       <c r="P6" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7059,7 +9077,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="15" t="n">
         <v>46359</v>
@@ -7069,16 +9087,16 @@
         <v>木</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
@@ -7088,7 +9106,7 @@
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
       <c r="P7" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7096,7 +9114,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="15" t="n">
         <v>46360</v>
@@ -7106,16 +9124,16 @@
         <v>金</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
@@ -7125,7 +9143,7 @@
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
       <c r="P8" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7133,7 +9151,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="15" t="n">
         <v>46361</v>
@@ -7143,16 +9161,16 @@
         <v>土</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
@@ -7162,7 +9180,7 @@
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
       <c r="P9" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7170,7 +9188,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="15" t="n">
         <v>46362</v>
@@ -7180,16 +9198,16 @@
         <v>日</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
@@ -7199,7 +9217,7 @@
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
       <c r="P10" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7207,7 +9225,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="15" t="n">
         <v>46363</v>
@@ -7217,16 +9235,16 @@
         <v>月</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
@@ -7236,7 +9254,7 @@
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
       <c r="P11" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7244,7 +9262,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="15" t="n">
         <v>46364</v>
@@ -7254,16 +9272,16 @@
         <v>火</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
@@ -7273,7 +9291,7 @@
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
       <c r="P12" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7281,7 +9299,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>46365</v>
@@ -7291,16 +9309,16 @@
         <v>水</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
@@ -7310,7 +9328,7 @@
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
       <c r="P13" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7318,7 +9336,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>46365</v>
@@ -7328,16 +9346,16 @@
         <v>水</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
@@ -7347,7 +9365,7 @@
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
       <c r="P14" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7355,7 +9373,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" s="15" t="n">
         <v>46365</v>
@@ -7365,16 +9383,16 @@
         <v>水</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
@@ -7384,7 +9402,7 @@
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
       <c r="P15" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7392,7 +9410,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" s="15" t="n">
         <v>46365</v>
@@ -7402,16 +9420,16 @@
         <v>水</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
@@ -7421,7 +9439,7 @@
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
       <c r="P16" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7429,7 +9447,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" s="15" t="n">
         <v>46366</v>
@@ -7439,16 +9457,16 @@
         <v>木</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
@@ -7458,7 +9476,7 @@
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7466,7 +9484,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" s="15" t="n">
         <v>46367</v>
@@ -7476,16 +9494,16 @@
         <v>金</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
@@ -7495,7 +9513,7 @@
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
       <c r="P18" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7503,7 +9521,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" s="15" t="n">
         <v>46367</v>
@@ -7513,16 +9531,16 @@
         <v>金</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
@@ -7532,7 +9550,7 @@
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
       <c r="P19" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7540,7 +9558,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" s="15" t="n">
         <v>46368</v>
@@ -7550,16 +9568,16 @@
         <v>土</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
@@ -7569,7 +9587,7 @@
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
       <c r="P20" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7577,7 +9595,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" s="15" t="n">
         <v>46368</v>
@@ -7587,16 +9605,16 @@
         <v>土</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
@@ -7606,7 +9624,7 @@
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
       <c r="P21" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7614,7 +9632,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C22" s="15" t="n">
         <v>46369</v>
@@ -7624,16 +9642,16 @@
         <v>日</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
@@ -7643,7 +9661,7 @@
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
       <c r="P22" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7651,7 +9669,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" s="15" t="n">
         <v>46369</v>
@@ -7661,16 +9679,16 @@
         <v>日</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
@@ -7680,7 +9698,7 @@
       <c r="N23" s="17"/>
       <c r="O23" s="17"/>
       <c r="P23" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7688,7 +9706,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" s="15" t="n">
         <v>46370</v>
@@ -7698,16 +9716,16 @@
         <v>月</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
@@ -7717,7 +9735,7 @@
       <c r="N24" s="17"/>
       <c r="O24" s="17"/>
       <c r="P24" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7725,7 +9743,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" s="15" t="n">
         <v>46371</v>
@@ -7735,16 +9753,16 @@
         <v>火</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
@@ -7754,7 +9772,7 @@
       <c r="N25" s="17"/>
       <c r="O25" s="17"/>
       <c r="P25" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7762,7 +9780,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" s="15" t="n">
         <v>46371</v>
@@ -7772,16 +9790,16 @@
         <v>火</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
@@ -7791,7 +9809,7 @@
       <c r="N26" s="17"/>
       <c r="O26" s="17"/>
       <c r="P26" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7799,7 +9817,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C27" s="15" t="n">
         <v>46371</v>
@@ -7809,16 +9827,16 @@
         <v>火</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
@@ -7828,7 +9846,7 @@
       <c r="N27" s="17"/>
       <c r="O27" s="17"/>
       <c r="P27" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7836,7 +9854,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" s="15" t="n">
         <v>46372</v>
@@ -7846,16 +9864,16 @@
         <v>水</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I28" s="17"/>
       <c r="J28" s="17"/>
@@ -7865,7 +9883,7 @@
       <c r="N28" s="17"/>
       <c r="O28" s="17"/>
       <c r="P28" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7873,7 +9891,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C29" s="15" t="n">
         <v>46372</v>
@@ -7883,16 +9901,16 @@
         <v>水</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I29" s="17"/>
       <c r="J29" s="17"/>
@@ -7902,7 +9920,7 @@
       <c r="N29" s="17"/>
       <c r="O29" s="17"/>
       <c r="P29" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7910,7 +9928,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C30" s="15" t="n">
         <v>46373</v>
@@ -7920,16 +9938,16 @@
         <v>木</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I30" s="17"/>
       <c r="J30" s="17"/>
@@ -7939,7 +9957,7 @@
       <c r="N30" s="17"/>
       <c r="O30" s="17"/>
       <c r="P30" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7947,7 +9965,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C31" s="15" t="n">
         <v>46374</v>
@@ -7957,16 +9975,16 @@
         <v>金</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I31" s="17"/>
       <c r="J31" s="17"/>
@@ -7976,7 +9994,7 @@
       <c r="N31" s="17"/>
       <c r="O31" s="17"/>
       <c r="P31" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7984,7 +10002,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" s="15" t="n">
         <v>46374</v>
@@ -7994,16 +10012,16 @@
         <v>金</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I32" s="17"/>
       <c r="J32" s="17"/>
@@ -8013,7 +10031,7 @@
       <c r="N32" s="17"/>
       <c r="O32" s="17"/>
       <c r="P32" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8021,7 +10039,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33" s="15" t="n">
         <v>46374</v>
@@ -8031,16 +10049,16 @@
         <v>金</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I33" s="17"/>
       <c r="J33" s="17"/>
@@ -8050,7 +10068,7 @@
       <c r="N33" s="17"/>
       <c r="O33" s="17"/>
       <c r="P33" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8058,7 +10076,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C34" s="15" t="n">
         <v>46375</v>
@@ -8068,16 +10086,16 @@
         <v>土</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I34" s="17"/>
       <c r="J34" s="17"/>
@@ -8087,7 +10105,7 @@
       <c r="N34" s="17"/>
       <c r="O34" s="17"/>
       <c r="P34" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8095,7 +10113,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C35" s="15" t="n">
         <v>46375</v>
@@ -8105,16 +10123,16 @@
         <v>土</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I35" s="17"/>
       <c r="J35" s="17"/>
@@ -8124,7 +10142,7 @@
       <c r="N35" s="17"/>
       <c r="O35" s="17"/>
       <c r="P35" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8132,7 +10150,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C36" s="15" t="n">
         <v>46375</v>
@@ -8142,16 +10160,16 @@
         <v>土</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I36" s="17"/>
       <c r="J36" s="17"/>
@@ -8161,7 +10179,7 @@
       <c r="N36" s="17"/>
       <c r="O36" s="17"/>
       <c r="P36" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8169,7 +10187,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C37" s="15" t="n">
         <v>46375</v>
@@ -8179,16 +10197,16 @@
         <v>土</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I37" s="17"/>
       <c r="J37" s="17"/>
@@ -8198,7 +10216,7 @@
       <c r="N37" s="17"/>
       <c r="O37" s="17"/>
       <c r="P37" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8206,7 +10224,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C38" s="15" t="n">
         <v>46376</v>
@@ -8216,16 +10234,16 @@
         <v>日</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I38" s="17"/>
       <c r="J38" s="17"/>
@@ -8235,7 +10253,7 @@
       <c r="N38" s="17"/>
       <c r="O38" s="17"/>
       <c r="P38" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8243,7 +10261,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C39" s="15" t="n">
         <v>46376</v>
@@ -8253,16 +10271,16 @@
         <v>日</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I39" s="17"/>
       <c r="J39" s="17"/>
@@ -8272,7 +10290,7 @@
       <c r="N39" s="17"/>
       <c r="O39" s="17"/>
       <c r="P39" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8280,7 +10298,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C40" s="15" t="n">
         <v>46376</v>
@@ -8290,16 +10308,16 @@
         <v>日</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I40" s="17"/>
       <c r="J40" s="17"/>
@@ -8309,7 +10327,7 @@
       <c r="N40" s="17"/>
       <c r="O40" s="17"/>
       <c r="P40" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8317,7 +10335,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C41" s="15" t="n">
         <v>46377</v>
@@ -8327,16 +10345,16 @@
         <v>月</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H41" s="14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I41" s="17"/>
       <c r="J41" s="17"/>
@@ -8346,7 +10364,7 @@
       <c r="N41" s="17"/>
       <c r="O41" s="17"/>
       <c r="P41" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8354,7 +10372,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="15" t="n">
         <v>46377</v>
@@ -8364,16 +10382,16 @@
         <v>月</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I42" s="17"/>
       <c r="J42" s="17"/>
@@ -8383,7 +10401,7 @@
       <c r="N42" s="17"/>
       <c r="O42" s="17"/>
       <c r="P42" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8391,7 +10409,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="15" t="n">
         <v>46377</v>
@@ -8401,16 +10419,16 @@
         <v>月</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I43" s="17"/>
       <c r="J43" s="17"/>
@@ -8420,7 +10438,7 @@
       <c r="N43" s="17"/>
       <c r="O43" s="17"/>
       <c r="P43" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8428,7 +10446,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" s="15" t="n">
         <v>46377</v>
@@ -8438,16 +10456,16 @@
         <v>月</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I44" s="17"/>
       <c r="J44" s="17"/>
@@ -8457,7 +10475,7 @@
       <c r="N44" s="17"/>
       <c r="O44" s="17"/>
       <c r="P44" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8465,7 +10483,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C45" s="15" t="n">
         <v>46377</v>
@@ -8475,16 +10493,16 @@
         <v>月</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
@@ -8494,7 +10512,7 @@
       <c r="N45" s="17"/>
       <c r="O45" s="17"/>
       <c r="P45" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8502,7 +10520,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C46" s="15" t="n">
         <v>46378</v>
@@ -8512,16 +10530,16 @@
         <v>火</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
@@ -8531,7 +10549,7 @@
       <c r="N46" s="17"/>
       <c r="O46" s="17"/>
       <c r="P46" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8539,7 +10557,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C47" s="15" t="n">
         <v>46379</v>
@@ -8549,16 +10567,16 @@
         <v>水</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I47" s="17"/>
       <c r="J47" s="17"/>
@@ -8568,7 +10586,7 @@
       <c r="N47" s="17"/>
       <c r="O47" s="17"/>
       <c r="P47" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8576,7 +10594,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C48" s="15" t="n">
         <v>46379</v>
@@ -8586,16 +10604,16 @@
         <v>水</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17"/>
@@ -8605,7 +10623,7 @@
       <c r="N48" s="17"/>
       <c r="O48" s="17"/>
       <c r="P48" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8613,7 +10631,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C49" s="15" t="n">
         <v>46384</v>
@@ -8623,16 +10641,16 @@
         <v>月</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17"/>
@@ -8642,7 +10660,7 @@
       <c r="N49" s="17"/>
       <c r="O49" s="17"/>
       <c r="P49" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8912,6 +10930,1388 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="n">
+        <f aca="false">G2-WEEKDAY(G2,3)</f>
+        <v>46321</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>46325</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="I2" s="19"/>
+      <c r="J2" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K2" s="19"/>
+      <c r="L2" s="13" t="n">
+        <f aca="true">IF(J2="完了","",G2-TODAY())</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="n">
+        <f aca="false">G3-WEEKDAY(G3,3)</f>
+        <v>46321</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>46358</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>46325</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I3" s="19"/>
+      <c r="J3" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K3" s="19"/>
+      <c r="L3" s="13" t="n">
+        <f aca="true">IF(J3="完了","",G3-TODAY())</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="n">
+        <f aca="false">G4-WEEKDAY(G4,3)</f>
+        <v>46321</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>46358</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>46325</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="I4" s="19"/>
+      <c r="J4" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K4" s="19"/>
+      <c r="L4" s="13" t="n">
+        <f aca="true">IF(J4="完了","",G4-TODAY())</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="n">
+        <f aca="false">G5-WEEKDAY(G5,3)</f>
+        <v>46321</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>46359</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>46327</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="I5" s="19"/>
+      <c r="J5" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K5" s="19"/>
+      <c r="L5" s="13" t="n">
+        <f aca="true">IF(J5="完了","",G5-TODAY())</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="n">
+        <f aca="false">G6-WEEKDAY(G6,3)</f>
+        <v>46321</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>46327</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I6" s="19"/>
+      <c r="J6" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K6" s="19"/>
+      <c r="L6" s="13" t="n">
+        <f aca="true">IF(J6="完了","",G6-TODAY())</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="20" t="n">
+        <f aca="false">G7-WEEKDAY(G7,3)</f>
+        <v>46321</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>46327</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" s="19"/>
+      <c r="J7" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K7" s="19"/>
+      <c r="L7" s="13" t="n">
+        <f aca="true">IF(J7="完了","",G7-TODAY())</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="20" t="n">
+        <f aca="false">G8-WEEKDAY(G8,3)</f>
+        <v>46321</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>46327</v>
+      </c>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K8" s="19"/>
+      <c r="L8" s="13" t="n">
+        <f aca="true">IF(J8="完了","",G8-TODAY())</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="20" t="n">
+        <f aca="false">G9-WEEKDAY(G9,3)</f>
+        <v>46328</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>46360</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>46330</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="I9" s="19"/>
+      <c r="J9" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K9" s="19"/>
+      <c r="L9" s="13" t="n">
+        <f aca="true">IF(J9="完了","",G9-TODAY())</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="20" t="n">
+        <f aca="false">G10-WEEKDAY(G10,3)</f>
+        <v>46328</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>46360</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>46330</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="I10" s="19"/>
+      <c r="J10" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K10" s="19"/>
+      <c r="L10" s="13" t="n">
+        <f aca="true">IF(J10="完了","",G10-TODAY())</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20" t="n">
+        <f aca="false">G11-WEEKDAY(G11,3)</f>
+        <v>46328</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>46375</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>46332</v>
+      </c>
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K11" s="19"/>
+      <c r="L11" s="13" t="n">
+        <f aca="true">IF(J11="完了","",G11-TODAY())</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="20" t="n">
+        <f aca="false">G12-WEEKDAY(G12,3)</f>
+        <v>46328</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>46360</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>46332</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="I12" s="19"/>
+      <c r="J12" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K12" s="19"/>
+      <c r="L12" s="13" t="n">
+        <f aca="true">IF(J12="完了","",G12-TODAY())</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="20" t="n">
+        <f aca="false">G13-WEEKDAY(G13,3)</f>
+        <v>46328</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>46367</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>46334</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K13" s="19"/>
+      <c r="L13" s="13" t="n">
+        <f aca="true">IF(J13="完了","",G13-TODAY())</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="20" t="n">
+        <f aca="false">G14-WEEKDAY(G14,3)</f>
+        <v>46328</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>46364</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>46334</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="I14" s="19"/>
+      <c r="J14" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K14" s="19"/>
+      <c r="L14" s="13" t="n">
+        <f aca="true">IF(J14="完了","",G14-TODAY())</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="20" t="n">
+        <f aca="false">G15-WEEKDAY(G15,3)</f>
+        <v>46335</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>46360</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>46339</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="I15" s="19"/>
+      <c r="J15" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K15" s="19"/>
+      <c r="L15" s="13" t="n">
+        <f aca="true">IF(J15="完了","",G15-TODAY())</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="20" t="n">
+        <f aca="false">G16-WEEKDAY(G16,3)</f>
+        <v>46335</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>46360</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>46341</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="I16" s="19"/>
+      <c r="J16" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K16" s="19"/>
+      <c r="L16" s="13" t="n">
+        <f aca="true">IF(J16="完了","",G16-TODAY())</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="20" t="n">
+        <f aca="false">G17-WEEKDAY(G17,3)</f>
+        <v>46335</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>46362</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>46341</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="I17" s="19"/>
+      <c r="J17" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K17" s="19"/>
+      <c r="L17" s="13" t="n">
+        <f aca="true">IF(J17="完了","",G17-TODAY())</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="20" t="n">
+        <f aca="false">G18-WEEKDAY(G18,3)</f>
+        <v>46335</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>46364</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>46341</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K18" s="19"/>
+      <c r="L18" s="13" t="n">
+        <f aca="true">IF(J18="完了","",G18-TODAY())</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="20" t="n">
+        <f aca="false">G19-WEEKDAY(G19,3)</f>
+        <v>46335</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>46365</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>46341</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K19" s="19"/>
+      <c r="L19" s="13" t="n">
+        <f aca="true">IF(J19="完了","",G19-TODAY())</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="20" t="n">
+        <f aca="false">G20-WEEKDAY(G20,3)</f>
+        <v>46342</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>46368</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>46346</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K20" s="19"/>
+      <c r="L20" s="13" t="n">
+        <f aca="true">IF(J20="完了","",G20-TODAY())</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="20" t="n">
+        <f aca="false">G21-WEEKDAY(G21,3)</f>
+        <v>46342</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>46358</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>46348</v>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K21" s="19"/>
+      <c r="L21" s="13" t="n">
+        <f aca="true">IF(J21="完了","",G21-TODAY())</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="20" t="n">
+        <f aca="false">G22-WEEKDAY(G22,3)</f>
+        <v>46342</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>46369</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>46348</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K22" s="19"/>
+      <c r="L22" s="13" t="n">
+        <f aca="true">IF(J22="完了","",G22-TODAY())</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="20" t="n">
+        <f aca="false">G23-WEEKDAY(G23,3)</f>
+        <v>46342</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>46372</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>46348</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="I23" s="19"/>
+      <c r="J23" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K23" s="19"/>
+      <c r="L23" s="13" t="n">
+        <f aca="true">IF(J23="完了","",G23-TODAY())</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="20" t="n">
+        <f aca="false">G24-WEEKDAY(G24,3)</f>
+        <v>46342</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>46367</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>46348</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K24" s="19"/>
+      <c r="L24" s="13" t="n">
+        <f aca="true">IF(J24="完了","",G24-TODAY())</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="20" t="n">
+        <f aca="false">G25-WEEKDAY(G25,3)</f>
+        <v>46342</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>46367</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>46348</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K25" s="19"/>
+      <c r="L25" s="13" t="n">
+        <f aca="true">IF(J25="完了","",G25-TODAY())</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="20" t="n">
+        <f aca="false">G26-WEEKDAY(G26,3)</f>
+        <v>46349</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>46365</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>46351</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K26" s="19"/>
+      <c r="L26" s="13" t="n">
+        <f aca="true">IF(J26="完了","",G26-TODAY())</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="20" t="n">
+        <f aca="false">G27-WEEKDAY(G27,3)</f>
+        <v>46349</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>46371</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>46353</v>
+      </c>
+      <c r="H27" s="17"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K27" s="19"/>
+      <c r="L27" s="13" t="n">
+        <f aca="true">IF(J27="完了","",G27-TODAY())</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="20" t="n">
+        <f aca="false">G28-WEEKDAY(G28,3)</f>
+        <v>46349</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>46365</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>46353</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K28" s="19"/>
+      <c r="L28" s="13" t="n">
+        <f aca="true">IF(J28="完了","",G28-TODAY())</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="20" t="n">
+        <f aca="false">G29-WEEKDAY(G29,3)</f>
+        <v>46349</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>46375</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>46353</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="I29" s="19"/>
+      <c r="J29" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K29" s="19"/>
+      <c r="L29" s="13" t="n">
+        <f aca="true">IF(J29="完了","",G29-TODAY())</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="20" t="n">
+        <f aca="false">G30-WEEKDAY(G30,3)</f>
+        <v>46349</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>46365</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>46353</v>
+      </c>
+      <c r="H30" s="17"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K30" s="19"/>
+      <c r="L30" s="13" t="n">
+        <f aca="true">IF(J30="完了","",G30-TODAY())</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="20" t="n">
+        <f aca="false">G31-WEEKDAY(G31,3)</f>
+        <v>46349</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>46353</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="I31" s="19"/>
+      <c r="J31" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K31" s="19"/>
+      <c r="L31" s="13" t="n">
+        <f aca="true">IF(J31="完了","",G31-TODAY())</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="20" t="n">
+        <f aca="false">G32-WEEKDAY(G32,3)</f>
+        <v>46349</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>46355</v>
+      </c>
+      <c r="H32" s="17"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K32" s="19"/>
+      <c r="L32" s="13" t="n">
+        <f aca="true">IF(J32="完了","",G32-TODAY())</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="20" t="n">
+        <f aca="false">G33-WEEKDAY(G33,3)</f>
+        <v>46356</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>46365</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>46362</v>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K33" s="19"/>
+      <c r="L33" s="13" t="n">
+        <f aca="true">IF(J33="完了","",G33-TODAY())</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="20" t="n">
+        <f aca="false">G34-WEEKDAY(G34,3)</f>
+        <v>46363</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>46375</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>46368</v>
+      </c>
+      <c r="H34" s="17"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K34" s="19"/>
+      <c r="L34" s="13" t="n">
+        <f aca="true">IF(J34="完了","",G34-TODAY())</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="20" t="n">
+        <f aca="false">G35-WEEKDAY(G35,3)</f>
+        <v>46370</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>46375</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>46372</v>
+      </c>
+      <c r="H35" s="17"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K35" s="19"/>
+      <c r="L35" s="13" t="n">
+        <f aca="true">IF(J35="完了","",G35-TODAY())</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="20" t="n">
+        <f aca="false">G36-WEEKDAY(G36,3)</f>
+        <v>46370</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>46375</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>46372</v>
+      </c>
+      <c r="H36" s="17"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K36" s="19"/>
+      <c r="L36" s="13" t="n">
+        <f aca="true">IF(J36="完了","",G36-TODAY())</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="20" t="n">
+        <f aca="false">G37-WEEKDAY(G37,3)</f>
+        <v>46370</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>46375</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>46372</v>
+      </c>
+      <c r="H37" s="17"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K37" s="19"/>
+      <c r="L37" s="13" t="n">
+        <f aca="true">IF(J37="完了","",G37-TODAY())</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="20" t="n">
+        <f aca="false">G38-WEEKDAY(G38,3)</f>
+        <v>46370</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>46375</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>46373</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="I38" s="19"/>
+      <c r="J38" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K38" s="19"/>
+      <c r="L38" s="13" t="n">
+        <f aca="true">IF(J38="完了","",G38-TODAY())</f>
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L38"/>
+  <conditionalFormatting sqref="A2:L38">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>$J2="完了"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND($J2&lt;&gt;"完了",$G2&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>AND($J2&lt;&gt;"完了",$G2-TODAY()&lt;=3,$G2&gt;=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J38" type="list">
+      <formula1>"未着手,進行中,完了,保留"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -8923,240 +12323,240 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>127</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>129</v>
+      <c r="A2" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>230</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>130</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>132</v>
+      <c r="A3" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>233</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>133</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>136</v>
+      <c r="A4" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="D5" s="21" t="s">
+      <c r="A5" s="23" t="s">
         <v>53</v>
       </c>
+      <c r="B5" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>141</v>
+      <c r="A6" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>143</v>
+      <c r="A7" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>244</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>144</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>146</v>
+      <c r="A8" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>247</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>147</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>150</v>
+      <c r="A9" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>153</v>
+      <c r="A10" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>156</v>
+      <c r="A11" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>159</v>
+      <c r="A12" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>161</v>
+      <c r="A13" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>262</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>162</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>165</v>
+      <c r="A14" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>101</v>
+      <c r="A15" s="23" t="s">
+        <v>102</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>167</v>
+        <v>267</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>268</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>170</v>
+      <c r="A16" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>173</v>
+      <c r="A17" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -9170,7 +12570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -9186,380 +12586,380 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>175</v>
+        <v>276</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>176</v>
+        <v>277</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>177</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>179</v>
+      <c r="A2" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>280</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="12" t="s">
-        <v>180</v>
+        <v>281</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>181</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>182</v>
+      <c r="A3" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>283</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>184</v>
+        <v>284</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>185</v>
+      <c r="A4" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>286</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>187</v>
+        <v>287</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>188</v>
+      <c r="A5" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>289</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>190</v>
+        <v>290</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>191</v>
+      <c r="A6" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>292</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>193</v>
+        <v>293</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>195</v>
+      <c r="A7" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>296</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="12" t="s">
-        <v>196</v>
+        <v>297</v>
       </c>
       <c r="E7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>197</v>
+      <c r="A8" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>298</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>198</v>
+        <v>299</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>198</v>
+        <v>299</v>
       </c>
       <c r="E8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>199</v>
+      <c r="A9" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>300</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="E9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>201</v>
+      <c r="A10" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>302</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="10" t="s">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="E10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>203</v>
+      <c r="A11" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>304</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="12" t="s">
-        <v>204</v>
+        <v>305</v>
       </c>
       <c r="E11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>205</v>
+      <c r="A12" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>306</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>207</v>
+        <v>307</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>208</v>
+      <c r="A13" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>309</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="10" t="s">
-        <v>209</v>
+        <v>310</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>210</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>211</v>
+      <c r="A14" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>312</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="10" t="s">
-        <v>212</v>
+        <v>313</v>
       </c>
       <c r="E14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>213</v>
+      <c r="A15" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>314</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="12"/>
-      <c r="E15" s="21" t="s">
-        <v>214</v>
+      <c r="E15" s="24" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>215</v>
+      <c r="A16" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>316</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>217</v>
+        <v>317</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>219</v>
+      <c r="A17" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>320</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>220</v>
+        <v>321</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>220</v>
+        <v>321</v>
       </c>
       <c r="E17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>221</v>
+      <c r="A18" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>322</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>222</v>
+        <v>323</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>222</v>
+        <v>323</v>
       </c>
       <c r="E18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>223</v>
+      <c r="A19" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>324</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>224</v>
+        <v>325</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>224</v>
+        <v>325</v>
       </c>
       <c r="E19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>226</v>
+      <c r="A20" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>327</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="12" t="s">
-        <v>227</v>
+        <v>328</v>
       </c>
       <c r="E20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>228</v>
+      <c r="A21" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>329</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="12" t="s">
-        <v>229</v>
+        <v>330</v>
       </c>
       <c r="E21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>230</v>
+      <c r="A22" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>331</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="12" t="s">
-        <v>227</v>
+        <v>328</v>
       </c>
       <c r="E22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>231</v>
+      <c r="A23" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>332</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="12" t="s">
-        <v>227</v>
+        <v>328</v>
       </c>
       <c r="E23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>232</v>
+      <c r="A24" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>333</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="12" t="s">
-        <v>227</v>
+        <v>328</v>
       </c>
       <c r="E24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>233</v>
+      <c r="A25" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>334</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="12" t="s">
-        <v>227</v>
+        <v>328</v>
       </c>
       <c r="E25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>235</v>
+      <c r="A26" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>336</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="E26" s="21" t="s">
-        <v>237</v>
+        <v>337</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>238</v>
+      <c r="A27" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>339</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="12"/>
@@ -9576,7 +12976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -9595,805 +12995,805 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>239</v>
+        <v>340</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>240</v>
+        <v>341</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>241</v>
+        <v>342</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>242</v>
+        <v>343</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>243</v>
+        <v>344</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>244</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>245</v>
+        <v>346</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>246</v>
+        <v>347</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>248</v>
+        <v>349</v>
       </c>
       <c r="B3" s="16" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>249</v>
+        <v>350</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>250</v>
+        <v>351</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>251</v>
+        <v>352</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>252</v>
+        <v>353</v>
       </c>
       <c r="G3" s="17"/>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>248</v>
+        <v>349</v>
       </c>
       <c r="B4" s="16" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>253</v>
+        <v>354</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>254</v>
+        <v>355</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>251</v>
+        <v>352</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>255</v>
+        <v>356</v>
       </c>
       <c r="G4" s="17"/>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>248</v>
+        <v>349</v>
       </c>
       <c r="B5" s="16" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>256</v>
+        <v>357</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>257</v>
+        <v>358</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>251</v>
+        <v>352</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>258</v>
+        <v>359</v>
       </c>
       <c r="G5" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>248</v>
+        <v>349</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>259</v>
+        <v>360</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>260</v>
+        <v>361</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>251</v>
+        <v>352</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>261</v>
+        <v>362</v>
       </c>
       <c r="G6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>248</v>
+        <v>349</v>
       </c>
       <c r="B7" s="16" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>262</v>
+        <v>363</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>263</v>
+        <v>364</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>251</v>
+        <v>352</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>261</v>
+        <v>362</v>
       </c>
       <c r="G7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>248</v>
+        <v>349</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>264</v>
+        <v>365</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>265</v>
+        <v>366</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>251</v>
+        <v>352</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>261</v>
+        <v>362</v>
       </c>
       <c r="G8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>267</v>
+        <v>368</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>268</v>
+        <v>369</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>269</v>
+        <v>370</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>271</v>
+        <v>372</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>272</v>
+        <v>373</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>269</v>
+        <v>370</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>273</v>
+        <v>374</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>274</v>
+        <v>375</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>4</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>275</v>
+        <v>376</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>276</v>
+        <v>377</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>5</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>278</v>
+        <v>379</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>269</v>
+        <v>370</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>6</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>279</v>
+        <v>380</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>280</v>
+        <v>381</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>269</v>
+        <v>370</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>281</v>
+        <v>382</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>282</v>
+        <v>383</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>8</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>283</v>
+        <v>384</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>284</v>
+        <v>385</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>269</v>
+        <v>370</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>9</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>285</v>
+        <v>386</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>286</v>
+        <v>387</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>269</v>
+        <v>370</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>287</v>
+        <v>388</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>288</v>
+        <v>389</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>269</v>
+        <v>370</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>11</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>290</v>
+        <v>391</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>291</v>
+        <v>392</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>292</v>
+        <v>393</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B21" s="16" t="n">
         <v>13</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>293</v>
+        <v>394</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>294</v>
+        <v>395</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>269</v>
+        <v>370</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B22" s="16" t="n">
         <v>14</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>295</v>
+        <v>396</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>296</v>
+        <v>397</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B23" s="16" t="n">
         <v>15</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>297</v>
+        <v>398</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>298</v>
+        <v>399</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B24" s="16" t="n">
         <v>16</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>299</v>
+        <v>400</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>300</v>
+        <v>401</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B25" s="16" t="n">
         <v>17</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>301</v>
+        <v>402</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>302</v>
+        <v>403</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B26" s="16" t="n">
         <v>18</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>303</v>
+        <v>404</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>304</v>
+        <v>405</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B27" s="16" t="n">
         <v>19</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>305</v>
+        <v>406</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>306</v>
+        <v>407</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>269</v>
+        <v>370</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B28" s="16" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>307</v>
+        <v>408</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>308</v>
+        <v>409</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G28" s="17"/>
     </row>
     <row r="29" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B29" s="16" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>309</v>
+        <v>410</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>310</v>
+        <v>411</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G29" s="17"/>
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>22</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>311</v>
+        <v>412</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>312</v>
+        <v>413</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G30" s="17"/>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B31" s="16" t="n">
         <v>23</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>313</v>
+        <v>414</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>314</v>
+        <v>415</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>269</v>
+        <v>370</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G31" s="17"/>
     </row>
     <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B32" s="16" t="n">
         <v>24</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>315</v>
+        <v>416</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>316</v>
+        <v>417</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G32" s="17"/>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B33" s="16" t="n">
         <v>25</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>317</v>
+        <v>418</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>318</v>
+        <v>419</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G33" s="17"/>
     </row>
     <row r="34" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B34" s="16" t="n">
         <v>26</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>319</v>
+        <v>420</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>320</v>
+        <v>421</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G34" s="17"/>
     </row>
     <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B35" s="16" t="n">
         <v>27</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>321</v>
+        <v>422</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>322</v>
+        <v>423</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G35" s="17"/>
     </row>
     <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B36" s="16" t="n">
         <v>28</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>323</v>
+        <v>424</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>324</v>
+        <v>425</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G36" s="17"/>
     </row>
     <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B37" s="16" t="n">
         <v>29</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>326</v>
+        <v>427</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>327</v>
+        <v>428</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G37" s="17"/>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="B38" s="16" t="n">
         <v>30</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>328</v>
+        <v>429</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>329</v>
+        <v>430</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>327</v>
+        <v>428</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>270</v>
+        <v>371</v>
       </c>
       <c r="G38" s="17"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="20" t="s">
-        <v>330</v>
+      <c r="C40" s="23" t="s">
+        <v>431</v>
       </c>
       <c r="D40" s="13" t="n">
         <f aca="false">COUNTIFS(A3:A38,"参加特典",C3:C38,"&lt;&gt;")</f>
@@ -10412,7 +13812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -10433,71 +13833,71 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>331</v>
+        <v>432</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>332</v>
+        <v>433</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>333</v>
+        <v>434</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>334</v>
+        <v>435</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>335</v>
+        <v>436</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>336</v>
+        <v>437</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>337</v>
+        <v>438</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>338</v>
+        <v>439</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>339</v>
+        <v>440</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>340</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>341</v>
+        <v>442</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>342</v>
+        <v>443</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>343</v>
+        <v>444</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>344</v>
+        <v>445</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>345</v>
+        <v>446</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>346</v>
+        <v>447</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>347</v>
+        <v>448</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>348</v>
+        <v>449</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>349</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>350</v>
+        <v>451</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -10511,7 +13911,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>351</v>
+        <v>452</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -10525,7 +13925,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>352</v>
+        <v>453</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -10539,7 +13939,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>353</v>
+        <v>454</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -10553,7 +13953,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>354</v>
+        <v>455</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -10567,7 +13967,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>355</v>
+        <v>456</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -10581,7 +13981,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>356</v>
+        <v>457</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -10595,7 +13995,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>357</v>
+        <v>458</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -10624,7 +14024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -10643,53 +14043,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>358</v>
+        <v>459</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>359</v>
+        <v>460</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>360</v>
+        <v>461</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>361</v>
+        <v>462</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>362</v>
+        <v>463</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>363</v>
+        <v>464</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>364</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>365</v>
+        <v>466</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>366</v>
+        <v>467</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>367</v>
+        <v>468</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>368</v>
+        <v>469</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>227</v>
+        <v>328</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>369</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>370</v>
+        <v>471</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -10700,7 +14100,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>371</v>
+        <v>472</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -10711,7 +14111,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>372</v>
+        <v>473</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -10722,7 +14122,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>373</v>
+        <v>474</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -10733,7 +14133,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>374</v>
+        <v>475</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -10744,7 +14144,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>375</v>
+        <v>476</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -10755,7 +14155,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>376</v>
+        <v>477</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -10766,7 +14166,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>377</v>
+        <v>478</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -10777,7 +14177,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>378</v>
+        <v>479</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -10788,7 +14188,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>379</v>
+        <v>480</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -10799,7 +14199,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>380</v>
+        <v>481</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -10810,7 +14210,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>381</v>
+        <v>482</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -10821,7 +14221,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>382</v>
+        <v>483</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -10832,7 +14232,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>383</v>
+        <v>484</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -10843,7 +14243,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>384</v>
+        <v>485</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -10854,7 +14254,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>385</v>
+        <v>486</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -10865,7 +14265,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>386</v>
+        <v>487</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -10876,7 +14276,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>387</v>
+        <v>488</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -10887,7 +14287,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>388</v>
+        <v>489</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -10898,7 +14298,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>389</v>
+        <v>490</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
